--- a/SuppXLS/Scen_DemProj_SETs.xlsx
+++ b/SuppXLS/Scen_DemProj_SETs.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduumb-my.sharepoint.com/personal/meselu_tegenie_mellaku_nmbu_no/Documents/Documents/GitHub/MANU2025/SuppXLS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{6B4276BF-FDF4-447C-8DCC-5FECEAB73AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C53FE082-898C-45CC-A3D4-6B4B479007CF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987A0130-A0D3-4A07-B93C-55FA88A7FDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BY_Data" sheetId="6" r:id="rId1"/>
-    <sheet name="CAR_Dem" sheetId="2" r:id="rId2"/>
+    <sheet name="MANENERGY_Dem" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -564,10 +564,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -856,13 +852,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:I6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
@@ -873,7 +869,7 @@
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
     </row>
-    <row r="3" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="7" t="s">
         <v>10</v>
       </c>
@@ -899,7 +895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>12</v>
       </c>
@@ -919,7 +915,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>12</v>
       </c>
@@ -939,7 +935,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>12</v>
       </c>
@@ -969,23 +965,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
-    <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
+    <col min="7" max="7" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="21.6" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -994,7 +990,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
@@ -1017,7 +1013,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
         <v>7</v>
       </c>
@@ -1035,7 +1031,7 @@
         <v>0.184</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
         <v>7</v>
       </c>
@@ -1053,7 +1049,7 @@
         <v>0.22900000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>7</v>
       </c>
@@ -1071,7 +1067,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
         <v>7</v>
       </c>
@@ -1087,7 +1083,7 @@
       </c>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
         <v>7</v>
       </c>
@@ -1102,7 +1098,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D9" s="15" t="s">
         <v>7</v>
       </c>
@@ -1117,7 +1113,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
         <v>7</v>
       </c>
@@ -1132,7 +1128,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
         <v>7</v>
       </c>
@@ -1147,7 +1143,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
         <v>7</v>
       </c>
@@ -1162,7 +1158,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
         <v>7</v>
       </c>
@@ -1177,7 +1173,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
         <v>7</v>
       </c>
@@ -1192,7 +1188,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
         <v>7</v>
       </c>
@@ -1207,7 +1203,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
         <v>7</v>
       </c>
@@ -1222,7 +1218,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
         <v>7</v>
       </c>
@@ -1237,7 +1233,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
         <v>7</v>
       </c>
@@ -1252,7 +1248,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
         <v>7</v>
       </c>
@@ -1267,7 +1263,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
         <v>7</v>
       </c>
@@ -1282,7 +1278,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
         <v>7</v>
       </c>

--- a/SuppXLS/Scen_DemProj_SETs.xlsx
+++ b/SuppXLS/Scen_DemProj_SETs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987A0130-A0D3-4A07-B93C-55FA88A7FDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC06352-7C55-44CB-AE75-9E51ADCD39CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BY_Data" sheetId="6" r:id="rId1"/>
@@ -909,6 +909,7 @@
         <v>2022</v>
       </c>
       <c r="H4" s="11">
+        <f>2861.5612011471*1</f>
         <v>2861.5612011470998</v>
       </c>
       <c r="I4" t="s">
@@ -929,7 +930,8 @@
         <v>2022</v>
       </c>
       <c r="H5">
-        <v>2605.1202084096003</v>
+        <f>2605.1202084096*0.8</f>
+        <v>2084.0961667276802</v>
       </c>
       <c r="I5" t="s">
         <v>16</v>
@@ -949,7 +951,8 @@
         <v>2022</v>
       </c>
       <c r="H6">
-        <v>7676.2275585426005</v>
+        <f>7676.2275585426*0.56</f>
+        <v>4298.6874327838559</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -1122,7 +1125,7 @@
       </c>
       <c r="F10" s="12">
         <f>BY_Data!H$5*(1+$J$4)^(E10-2022)</f>
-        <v>4323.9720195382133</v>
+        <v>3459.1776156305709</v>
       </c>
       <c r="G10" s="14" t="s">
         <v>16</v>
@@ -1137,7 +1140,7 @@
       </c>
       <c r="F11" s="12">
         <f>F10*(1+$J$5)^(E11-2025)</f>
-        <v>12123.898431771198</v>
+        <v>9699.1187454169594</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>16</v>
@@ -1152,7 +1155,7 @@
       </c>
       <c r="F12" s="12">
         <f>F$11*(1+$J$6)^(E12-2030)</f>
-        <v>19085.910602447733</v>
+        <v>15268.728481958189</v>
       </c>
       <c r="G12" s="14" t="s">
         <v>16</v>
@@ -1167,7 +1170,7 @@
       </c>
       <c r="F13" s="12">
         <f t="shared" ref="F13:F15" si="1">F$11*(1+$J$6)^(E13-2030)</f>
-        <v>30045.779876383363</v>
+        <v>24036.623901106694</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>16</v>
@@ -1182,7 +1185,7 @@
       </c>
       <c r="F14" s="12">
         <f t="shared" si="1"/>
-        <v>47299.230682989124</v>
+        <v>37839.384546391302</v>
       </c>
       <c r="G14" s="14" t="s">
         <v>16</v>
@@ -1197,7 +1200,7 @@
       </c>
       <c r="F15" s="12">
         <f t="shared" si="1"/>
-        <v>74460.281357553366</v>
+        <v>59568.225086042694</v>
       </c>
       <c r="G15" s="14" t="s">
         <v>16</v>
@@ -1212,7 +1215,7 @@
       </c>
       <c r="F16" s="12">
         <f>BY_Data!H$6*(1+$J$4)^(E16-2022)</f>
-        <v>12740.98334180502</v>
+        <v>7134.9506714108102</v>
       </c>
       <c r="G16" s="14" t="s">
         <v>17</v>
@@ -1227,7 +1230,7 @@
       </c>
       <c r="F17" s="12">
         <f>F16*(1+$J$5)^(E17-2025)</f>
-        <v>35724.187681822645</v>
+        <v>20005.54510182068</v>
       </c>
       <c r="G17" s="14" t="s">
         <v>17</v>
@@ -1242,7 +1245,7 @@
       </c>
       <c r="F18" s="12">
         <f>F$17*(1+$J$6)^(E18-2030)</f>
-        <v>56238.400237135786</v>
+        <v>31493.504132796039</v>
       </c>
       <c r="G18" s="14" t="s">
         <v>17</v>
@@ -1257,7 +1260,7 @@
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F21" si="2">F$17*(1+$J$6)^(E19-2030)</f>
-        <v>88532.668381472104</v>
+        <v>49578.294293624378</v>
       </c>
       <c r="G19" s="14" t="s">
         <v>17</v>
@@ -1272,7 +1275,7 @@
       </c>
       <c r="F20" s="12">
         <f t="shared" si="2"/>
-        <v>139371.5564044092</v>
+        <v>78048.071586469145</v>
       </c>
       <c r="G20" s="14" t="s">
         <v>17</v>
@@ -1287,7 +1290,7 @@
       </c>
       <c r="F21" s="12">
         <f t="shared" si="2"/>
-        <v>219404.10347614138</v>
+        <v>122866.29794663917</v>
       </c>
       <c r="G21" s="14" t="s">
         <v>17</v>
